--- a/数据源/result_data_special.xlsx
+++ b/数据源/result_data_special.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12080"/>
+    <workbookView windowWidth="29868" windowHeight="13380"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="922" uniqueCount="448">
   <si>
     <t>vg_object_id</t>
   </si>
@@ -89,6 +89,12 @@
     <t>prompt</t>
   </si>
   <si>
+    <t>picture_id</t>
+  </si>
+  <si>
+    <t>question_id</t>
+  </si>
+  <si>
     <t>sheep</t>
   </si>
   <si>
@@ -128,6 +134,9 @@
     <t>这是一只____。</t>
   </si>
   <si>
+    <t>rds-1</t>
+  </si>
+  <si>
     <t>cow</t>
   </si>
   <si>
@@ -158,6 +167,9 @@
     <t>这是一头____。</t>
   </si>
   <si>
+    <t>rds-2</t>
+  </si>
+  <si>
     <t>man</t>
   </si>
   <si>
@@ -191,6 +203,9 @@
     <t>这是一位____。</t>
   </si>
   <si>
+    <t>rds-3</t>
+  </si>
+  <si>
     <t>kid</t>
   </si>
   <si>
@@ -215,6 +230,9 @@
     <t>[159, 76, 189, 423]</t>
   </si>
   <si>
+    <t>rds-4</t>
+  </si>
+  <si>
     <t>bird</t>
   </si>
   <si>
@@ -236,6 +254,9 @@
     <t>[7, 65, 224, 371]</t>
   </si>
   <si>
+    <t>rds-5</t>
+  </si>
+  <si>
     <t>{'羊': 16, '羊羔': 1, '绵羊': 1, '羊肉': 1}</t>
   </si>
   <si>
@@ -248,6 +269,9 @@
     <t>[71, 164, 275, 145]</t>
   </si>
   <si>
+    <t>rds-6</t>
+  </si>
+  <si>
     <t>puppy</t>
   </si>
   <si>
@@ -272,6 +296,9 @@
     <t>[36, 79, 261, 254]</t>
   </si>
   <si>
+    <t>rds-7</t>
+  </si>
+  <si>
     <t>{'鸟': 14, '鹤': 3, '鹭': 1, '丹顶鹤': 1, '鸟类动物': 1, '鹳': 1}</t>
   </si>
   <si>
@@ -287,6 +314,9 @@
     <t>[56, 66, 222, 365]</t>
   </si>
   <si>
+    <t>rds-8</t>
+  </si>
+  <si>
     <t>peacock</t>
   </si>
   <si>
@@ -305,6 +335,9 @@
     <t>[21, 56, 146, 442]</t>
   </si>
   <si>
+    <t>rds-9</t>
+  </si>
+  <si>
     <t>{'bird': 27, 'parrot': 3, 'conure': 1}</t>
   </si>
   <si>
@@ -317,6 +350,9 @@
     <t>[158, 101, 261, 893]</t>
   </si>
   <si>
+    <t>rds-10</t>
+  </si>
+  <si>
     <t>hen</t>
   </si>
   <si>
@@ -335,6 +371,9 @@
     <t>[2, 1, 310, 497]</t>
   </si>
   <si>
+    <t>rds-11</t>
+  </si>
+  <si>
     <t>woman</t>
   </si>
   <si>
@@ -350,6 +389,9 @@
     <t>[0, 83, 325, 417]</t>
   </si>
   <si>
+    <t>rds-12</t>
+  </si>
+  <si>
     <t>dove</t>
   </si>
   <si>
@@ -371,6 +413,9 @@
     <t>[88, 113, 341, 256]</t>
   </si>
   <si>
+    <t>rds-13</t>
+  </si>
+  <si>
     <t>pitcher</t>
   </si>
   <si>
@@ -389,6 +434,9 @@
     <t>[143, 54, 229, 272]</t>
   </si>
   <si>
+    <t>rds-14</t>
+  </si>
+  <si>
     <t>{'bird': 29, 'seagull': 4}</t>
   </si>
   <si>
@@ -398,6 +446,9 @@
     <t>[6, 60, 322, 265]</t>
   </si>
   <si>
+    <t>rds-15</t>
+  </si>
+  <si>
     <t>cat</t>
   </si>
   <si>
@@ -413,6 +464,9 @@
     <t>[90, 11, 315, 323]</t>
   </si>
   <si>
+    <t>rds-16</t>
+  </si>
+  <si>
     <t>flower</t>
   </si>
   <si>
@@ -440,6 +494,9 @@
     <t>这是一朵____。</t>
   </si>
   <si>
+    <t>rds-17</t>
+  </si>
+  <si>
     <t>{'羊': 14, '养': 1, '绵阳': 1}</t>
   </si>
   <si>
@@ -452,6 +509,9 @@
     <t>[40, 91, 166, 283]</t>
   </si>
   <si>
+    <t>rds-18</t>
+  </si>
+  <si>
     <t>{'花': 12, '花苞': 1, '菊花': 3, '花朵': 6}</t>
   </si>
   <si>
@@ -464,6 +524,9 @@
     <t>[33, 76, 330, 189]</t>
   </si>
   <si>
+    <t>rds-19</t>
+  </si>
+  <si>
     <t>girl</t>
   </si>
   <si>
@@ -479,6 +542,9 @@
     <t>[0, 34, 212, 371]</t>
   </si>
   <si>
+    <t>rds-20</t>
+  </si>
+  <si>
     <t>dog</t>
   </si>
   <si>
@@ -491,6 +557,9 @@
     <t>[103, 68, 194, 270]</t>
   </si>
   <si>
+    <t>rds-21</t>
+  </si>
+  <si>
     <t>{'鸟': 18, '老</t>
   </si>
   <si>
@@ -503,6 +572,9 @@
     <t>[213, 57, 167, 212]</t>
   </si>
   <si>
+    <t>rds-22</t>
+  </si>
+  <si>
     <t>coat</t>
   </si>
   <si>
@@ -518,6 +590,9 @@
     <t>[179, 15, 269, 318]</t>
   </si>
   <si>
+    <t>rds-23</t>
+  </si>
+  <si>
     <t>{'牛': 13, '鹿': 2, '驴': 1, '牛蹄子': 1, '奶牛': 2}</t>
   </si>
   <si>
@@ -530,6 +605,9 @@
     <t>[259, 64, 238, 310]</t>
   </si>
   <si>
+    <t>rds-24</t>
+  </si>
+  <si>
     <t>{'花': 20, '向日葵': 1}</t>
   </si>
   <si>
@@ -542,6 +620,9 @@
     <t>[69, 0, 407, 411]</t>
   </si>
   <si>
+    <t>rds-25</t>
+  </si>
+  <si>
     <t>{'羊': 14, '山羊': 3, '绵羊': 1, '羊羔': 1, '动物': 1}</t>
   </si>
   <si>
@@ -554,6 +635,9 @@
     <t>[17, 170, 266, 162]</t>
   </si>
   <si>
+    <t>rds-26</t>
+  </si>
+  <si>
     <t>['狗']</t>
   </si>
   <si>
@@ -569,6 +653,9 @@
     <t>[192, 131, 706, 633]</t>
   </si>
   <si>
+    <t>rds-27</t>
+  </si>
+  <si>
     <t>{'花': 17, '话': 1, '花瓣': 1, '假花': 1}</t>
   </si>
   <si>
@@ -581,6 +668,9 @@
     <t>[290, 2, 174, 253]</t>
   </si>
   <si>
+    <t>rds-28</t>
+  </si>
+  <si>
     <t>{'cat': 35, 'animal': 1}</t>
   </si>
   <si>
@@ -593,6 +683,9 @@
     <t>[67, 55, 287, 310]</t>
   </si>
   <si>
+    <t>rds-29</t>
+  </si>
+  <si>
     <t>{'人': 4, '网球选手': 1, '网球运动员': 3, '大人': 1, '打网球': 1, '运动员': 7, '球员': 1, '网球员': 1}</t>
   </si>
   <si>
@@ -605,6 +698,9 @@
     <t>[182, 17, 258, 449]</t>
   </si>
   <si>
+    <t>rds-30</t>
+  </si>
+  <si>
     <t>desk</t>
   </si>
   <si>
@@ -632,6 +728,9 @@
     <t>这是一张____。</t>
   </si>
   <si>
+    <t>rds-31</t>
+  </si>
+  <si>
     <t>plane</t>
   </si>
   <si>
@@ -659,6 +758,9 @@
     <t>这是一架____。</t>
   </si>
   <si>
+    <t>rds-32</t>
+  </si>
+  <si>
     <t>airplane</t>
   </si>
   <si>
@@ -674,6 +776,9 @@
     <t>[43, 182, 334, 139]</t>
   </si>
   <si>
+    <t>rds-33</t>
+  </si>
+  <si>
     <t>dress</t>
   </si>
   <si>
@@ -704,6 +809,9 @@
     <t>这是一件____。</t>
   </si>
   <si>
+    <t>rds-34</t>
+  </si>
+  <si>
     <t>house.</t>
   </si>
   <si>
@@ -734,6 +842,9 @@
     <t>这是一栋____。</t>
   </si>
   <si>
+    <t>rds-35</t>
+  </si>
+  <si>
     <t>restaurant</t>
   </si>
   <si>
@@ -758,6 +869,9 @@
     <t>这是一间____。</t>
   </si>
   <si>
+    <t>rds-36</t>
+  </si>
+  <si>
     <t>bed</t>
   </si>
   <si>
@@ -782,6 +896,9 @@
     <t>[0, 258, 499, 241]</t>
   </si>
   <si>
+    <t>rds-37</t>
+  </si>
+  <si>
     <t>jet</t>
   </si>
   <si>
@@ -797,6 +914,9 @@
     <t>[186, 15, 312, 179]</t>
   </si>
   <si>
+    <t>rds-38</t>
+  </si>
+  <si>
     <t>cake</t>
   </si>
   <si>
@@ -815,6 +935,9 @@
     <t>这是一块____。</t>
   </si>
   <si>
+    <t>rds-39</t>
+  </si>
+  <si>
     <t>['桌子']</t>
   </si>
   <si>
@@ -830,6 +953,9 @@
     <t>[0, 127, 678, 468]</t>
   </si>
   <si>
+    <t>rds-40</t>
+  </si>
+  <si>
     <t>['婚纱']</t>
   </si>
   <si>
@@ -845,6 +971,9 @@
     <t>[134, 131, 321, 203]</t>
   </si>
   <si>
+    <t>rds-41</t>
+  </si>
+  <si>
     <t>['西装']</t>
   </si>
   <si>
@@ -863,6 +992,9 @@
     <t>[68, 203, 277, 294]</t>
   </si>
   <si>
+    <t>rds-42</t>
+  </si>
+  <si>
     <t>van</t>
   </si>
   <si>
@@ -887,6 +1019,9 @@
     <t>这是一辆____。</t>
   </si>
   <si>
+    <t>rds-43</t>
+  </si>
+  <si>
     <t>jacket</t>
   </si>
   <si>
@@ -902,6 +1037,9 @@
     <t>[0, 188, 338, 311]</t>
   </si>
   <si>
+    <t>rds-44</t>
+  </si>
+  <si>
     <t>pizza</t>
   </si>
   <si>
@@ -923,6 +1061,9 @@
     <t>[1, 109, 372, 348]</t>
   </si>
   <si>
+    <t>rds-45</t>
+  </si>
+  <si>
     <t>knife</t>
   </si>
   <si>
@@ -950,6 +1091,9 @@
     <t>这是一把____。</t>
   </si>
   <si>
+    <t>rds-46</t>
+  </si>
+  <si>
     <t>pasta</t>
   </si>
   <si>
@@ -974,6 +1118,9 @@
     <t>这是一份____。</t>
   </si>
   <si>
+    <t>rds-47</t>
+  </si>
+  <si>
     <t>truck</t>
   </si>
   <si>
@@ -989,6 +1136,9 @@
     <t>[25, 45, 448, 279]</t>
   </si>
   <si>
+    <t>rds-48</t>
+  </si>
+  <si>
     <t>counter</t>
   </si>
   <si>
@@ -1004,6 +1154,9 @@
     <t>[21, 330, 456, 148]</t>
   </si>
   <si>
+    <t>rds-49</t>
+  </si>
+  <si>
     <t>shirt</t>
   </si>
   <si>
@@ -1022,6 +1175,9 @@
     <t>[55, 154, 189, 310]</t>
   </si>
   <si>
+    <t>rds-50</t>
+  </si>
+  <si>
     <t>outhouse</t>
   </si>
   <si>
@@ -1046,6 +1202,9 @@
     <t>间</t>
   </si>
   <si>
+    <t>rds-51</t>
+  </si>
+  <si>
     <t>boat</t>
   </si>
   <si>
@@ -1070,6 +1229,9 @@
     <t>这是一艘____。</t>
   </si>
   <si>
+    <t>rds-52</t>
+  </si>
+  <si>
     <t>['裙子']</t>
   </si>
   <si>
@@ -1085,6 +1247,9 @@
     <t>[13, 293, 252, 205]</t>
   </si>
   <si>
+    <t>rds-53</t>
+  </si>
+  <si>
     <t>{'刀': 18, '刀子': 2, '菜刀': 1}</t>
   </si>
   <si>
@@ -1097,6 +1262,9 @@
     <t>[286, 37, 177, 411]</t>
   </si>
   <si>
+    <t>rds-54</t>
+  </si>
+  <si>
     <t>table</t>
   </si>
   <si>
@@ -1112,6 +1280,9 @@
     <t>[0, 360, 374, 139]</t>
   </si>
   <si>
+    <t>rds-55</t>
+  </si>
+  <si>
     <t>car</t>
   </si>
   <si>
@@ -1130,6 +1301,9 @@
     <t>[17, 50, 227, 213]</t>
   </si>
   <si>
+    <t>rds-56</t>
+  </si>
+  <si>
     <t>overpass</t>
   </si>
   <si>
@@ -1148,6 +1322,9 @@
     <t>[54, 0, 445, 208]</t>
   </si>
   <si>
+    <t>rds-57</t>
+  </si>
+  <si>
     <t>['警车']</t>
   </si>
   <si>
@@ -1157,6 +1334,9 @@
     <t>[148, 1, 352, 244]</t>
   </si>
   <si>
+    <t>rds-58</t>
+  </si>
+  <si>
     <t>{'车': 11, '跑车': 4, '轿车': 3, '汽车': 3}</t>
   </si>
   <si>
@@ -1172,6 +1352,9 @@
     <t>[0, 70, 220, 270]</t>
   </si>
   <si>
+    <t>rds-59</t>
+  </si>
+  <si>
     <t>house</t>
   </si>
   <si>
@@ -1185,6 +1368,9 @@
   </si>
   <si>
     <t>[3, 4, 216, 215]</t>
+  </si>
+  <si>
+    <t>rds-60</t>
   </si>
 </sst>
 </file>
@@ -1675,148 +1861,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2172,10 +2358,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T61"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <dimension ref="A1:W61"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:23">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2236,25 +2422,31 @@
       <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="V1" t="s">
+        <v>20</v>
+      </c>
+      <c r="W1" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="2" spans="1:20">
+    <row r="2" spans="1:23">
       <c r="A2">
         <v>2298362</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" t="s">
         <v>23</v>
-      </c>
-      <c r="F2" t="s">
-        <v>21</v>
       </c>
       <c r="G2">
         <v>10</v>
@@ -2269,54 +2461,60 @@
         <v>2.84535093662244</v>
       </c>
       <c r="K2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L2">
         <v>3.53229848484848</v>
       </c>
       <c r="M2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="Q2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="T2" t="s">
-        <v>32</v>
+        <v>34</v>
+      </c>
+      <c r="V2">
+        <v>1</v>
+      </c>
+      <c r="W2" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:20">
+    <row r="3" spans="1:23">
       <c r="A3">
         <v>3556707</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G3">
         <v>3</v>
@@ -2331,54 +2529,60 @@
         <v>0.678407090937567</v>
       </c>
       <c r="K3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L3">
         <v>3.20804782608696</v>
       </c>
       <c r="M3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="N3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="O3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="P3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="Q3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="T3" t="s">
-        <v>42</v>
+        <v>45</v>
+      </c>
+      <c r="V3">
+        <v>2</v>
+      </c>
+      <c r="W3" t="s">
+        <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:20">
+    <row r="4" spans="1:23">
       <c r="A4">
         <v>3960187</v>
       </c>
       <c r="B4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F4" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G4">
         <v>8</v>
@@ -2393,54 +2597,60 @@
         <v>2.58392594005366</v>
       </c>
       <c r="K4" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="L4">
         <v>4.02386818181818</v>
       </c>
       <c r="M4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="N4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="O4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="P4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="Q4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="T4" t="s">
-        <v>53</v>
+        <v>57</v>
+      </c>
+      <c r="V4">
+        <v>3</v>
+      </c>
+      <c r="W4" t="s">
+        <v>58</v>
       </c>
     </row>
-    <row r="5" spans="1:20">
+    <row r="5" spans="1:23">
       <c r="A5">
         <v>3273691</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E5" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F5" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G5">
         <v>9</v>
@@ -2455,54 +2665,60 @@
         <v>2.80004461847901</v>
       </c>
       <c r="K5" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="L5">
         <v>3.68278947368421</v>
       </c>
       <c r="M5" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="N5" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="O5" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="P5" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="Q5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S5" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="T5" t="s">
-        <v>53</v>
+        <v>57</v>
+      </c>
+      <c r="V5">
+        <v>4</v>
+      </c>
+      <c r="W5" t="s">
+        <v>67</v>
       </c>
     </row>
-    <row r="6" spans="1:20">
+    <row r="6" spans="1:23">
       <c r="A6">
         <v>3110275</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="E6" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="F6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G6">
         <v>4</v>
@@ -2517,54 +2733,60 @@
         <v>0.956765708366314</v>
       </c>
       <c r="K6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L6">
         <v>3.15304848484848</v>
       </c>
       <c r="M6" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="N6" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O6" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="P6" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="Q6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="T6" t="s">
-        <v>32</v>
+        <v>34</v>
+      </c>
+      <c r="V6">
+        <v>5</v>
+      </c>
+      <c r="W6" t="s">
+        <v>75</v>
       </c>
     </row>
-    <row r="7" spans="1:20">
+    <row r="7" spans="1:23">
       <c r="A7">
         <v>2637056</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E7" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="F7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G7">
         <v>4</v>
@@ -2579,54 +2801,60 @@
         <v>0.879506460812006</v>
       </c>
       <c r="K7" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="L7">
         <v>2.69493684210526</v>
       </c>
       <c r="M7" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="N7" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="O7" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="P7" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="Q7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="T7" t="s">
-        <v>32</v>
+        <v>34</v>
+      </c>
+      <c r="V7">
+        <v>6</v>
+      </c>
+      <c r="W7" t="s">
+        <v>80</v>
       </c>
     </row>
-    <row r="8" spans="1:20">
+    <row r="8" spans="1:23">
       <c r="A8">
         <v>3392338</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="E8" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F8" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G8">
         <v>6</v>
@@ -2641,54 +2869,60 @@
         <v>1.92192809488736</v>
       </c>
       <c r="K8" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="L8">
         <v>4.24697</v>
       </c>
       <c r="M8" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="N8" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="O8" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="Q8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="T8" t="s">
-        <v>32</v>
+        <v>34</v>
+      </c>
+      <c r="V8">
+        <v>7</v>
+      </c>
+      <c r="W8" t="s">
+        <v>89</v>
       </c>
     </row>
-    <row r="9" spans="1:20">
+    <row r="9" spans="1:23">
       <c r="A9">
         <v>2678297</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D9" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="E9" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="F9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G9">
         <v>6</v>
@@ -2703,54 +2937,60 @@
         <v>1.62765759368496</v>
       </c>
       <c r="K9" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="L9">
         <v>2.67830571428571</v>
       </c>
       <c r="M9" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="N9" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="O9" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="P9" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="Q9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R9" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S9" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="T9" t="s">
-        <v>32</v>
+        <v>34</v>
+      </c>
+      <c r="V9">
+        <v>8</v>
+      </c>
+      <c r="W9" t="s">
+        <v>95</v>
       </c>
     </row>
-    <row r="10" spans="1:20">
+    <row r="10" spans="1:23">
       <c r="A10">
         <v>3777606</v>
       </c>
       <c r="B10" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="E10" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="F10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G10">
         <v>6</v>
@@ -2765,54 +3005,60 @@
         <v>2.33379987011787</v>
       </c>
       <c r="K10" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L10">
         <v>4.26151739130435</v>
       </c>
       <c r="M10" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="N10" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="O10" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="P10" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="Q10" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R10" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="T10" t="s">
-        <v>32</v>
+        <v>34</v>
+      </c>
+      <c r="V10">
+        <v>9</v>
+      </c>
+      <c r="W10" t="s">
+        <v>102</v>
       </c>
     </row>
-    <row r="11" spans="1:20">
+    <row r="11" spans="1:23">
       <c r="A11">
         <v>146131</v>
       </c>
       <c r="B11" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D11" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="E11" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="F11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G11">
         <v>7</v>
@@ -2827,54 +3073,60 @@
         <v>1.99484144464497</v>
       </c>
       <c r="K11" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="L11">
         <v>3.99187894736842</v>
       </c>
       <c r="M11" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="N11" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="O11" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="P11" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="Q11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="T11" t="s">
-        <v>32</v>
+        <v>34</v>
+      </c>
+      <c r="V11">
+        <v>10</v>
+      </c>
+      <c r="W11" t="s">
+        <v>107</v>
       </c>
     </row>
-    <row r="12" spans="1:20">
+    <row r="12" spans="1:23">
       <c r="A12">
         <v>834928</v>
       </c>
       <c r="B12" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="C12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D12" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="E12" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="F12" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -2889,54 +3141,60 @@
         <v>1.60520670787491</v>
       </c>
       <c r="K12" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="L12">
         <v>4.39016071428571</v>
       </c>
       <c r="M12" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="N12" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="O12" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="P12" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="Q12" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R12" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S12" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="T12" t="s">
-        <v>32</v>
+        <v>34</v>
+      </c>
+      <c r="V12">
+        <v>11</v>
+      </c>
+      <c r="W12" t="s">
+        <v>114</v>
       </c>
     </row>
-    <row r="13" spans="1:20">
+    <row r="13" spans="1:23">
       <c r="A13">
         <v>3960820</v>
       </c>
       <c r="B13" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="C13" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D13" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E13" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="F13" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G13">
         <v>7</v>
@@ -2951,54 +3209,60 @@
         <v>2.24643934467102</v>
       </c>
       <c r="K13" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="L13">
         <v>4.24185166666667</v>
       </c>
       <c r="M13" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="N13" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="O13" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="P13" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="Q13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S13" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="T13" t="s">
-        <v>53</v>
+        <v>57</v>
+      </c>
+      <c r="V13">
+        <v>12</v>
+      </c>
+      <c r="W13" t="s">
+        <v>120</v>
       </c>
     </row>
-    <row r="14" spans="1:20">
+    <row r="14" spans="1:23">
       <c r="A14">
         <v>653443</v>
       </c>
       <c r="B14" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="C14" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D14" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="E14" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="F14" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G14">
         <v>7</v>
@@ -3013,54 +3277,60 @@
         <v>2.14402391075742</v>
       </c>
       <c r="K14" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="L14">
         <v>2.72906315789474</v>
       </c>
       <c r="M14" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="N14" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="O14" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="P14" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="Q14" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R14" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="T14" t="s">
-        <v>32</v>
+        <v>34</v>
+      </c>
+      <c r="V14">
+        <v>13</v>
+      </c>
+      <c r="W14" t="s">
+        <v>128</v>
       </c>
     </row>
-    <row r="15" spans="1:20">
+    <row r="15" spans="1:23">
       <c r="A15">
         <v>3627437</v>
       </c>
       <c r="B15" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="C15" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D15" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E15" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="F15" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G15">
         <v>10</v>
@@ -3075,54 +3345,60 @@
         <v>3.11583409216322</v>
       </c>
       <c r="K15" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="L15">
         <v>3.53840614035088</v>
       </c>
       <c r="M15" t="s">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="N15" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="O15" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="P15" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="Q15" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R15" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S15" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="T15" t="s">
-        <v>53</v>
+        <v>57</v>
+      </c>
+      <c r="V15">
+        <v>14</v>
+      </c>
+      <c r="W15" t="s">
+        <v>135</v>
       </c>
     </row>
-    <row r="16" spans="1:20">
+    <row r="16" spans="1:23">
       <c r="A16">
         <v>226061</v>
       </c>
       <c r="B16" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D16" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="E16" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="F16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G16">
         <v>2</v>
@@ -3137,54 +3413,60 @@
         <v>0.29747224891929</v>
       </c>
       <c r="K16" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="L16">
         <v>3.29276315789474</v>
       </c>
       <c r="M16" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="N16" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="O16" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="P16" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="Q16" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R16" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S16" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="T16" t="s">
-        <v>32</v>
+        <v>34</v>
+      </c>
+      <c r="V16">
+        <v>15</v>
+      </c>
+      <c r="W16" t="s">
+        <v>139</v>
       </c>
     </row>
-    <row r="17" spans="1:20">
+    <row r="17" spans="1:23">
       <c r="A17">
         <v>173748</v>
       </c>
       <c r="B17" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="C17" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D17" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="E17" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="F17" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -3199,54 +3481,60 @@
         <v>1.9393538721672</v>
       </c>
       <c r="K17" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="L17">
         <v>4.002925</v>
       </c>
       <c r="M17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="N17" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="O17" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="P17" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="Q17" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R17" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="T17" t="s">
-        <v>32</v>
+        <v>34</v>
+      </c>
+      <c r="V17">
+        <v>16</v>
+      </c>
+      <c r="W17" t="s">
+        <v>145</v>
       </c>
     </row>
-    <row r="18" spans="1:20">
+    <row r="18" spans="1:23">
       <c r="A18">
         <v>2746869</v>
       </c>
       <c r="B18" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="C18" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D18" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="E18" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="F18" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G18">
         <v>3</v>
@@ -3261,54 +3549,60 @@
         <v>0.59072391864065</v>
       </c>
       <c r="K18" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="L18">
         <v>3.9517</v>
       </c>
       <c r="M18" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="N18" t="s">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="O18" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="P18" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="Q18" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R18" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S18" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="T18" t="s">
-        <v>136</v>
+        <v>154</v>
+      </c>
+      <c r="V18">
+        <v>17</v>
+      </c>
+      <c r="W18" t="s">
+        <v>155</v>
       </c>
     </row>
-    <row r="19" spans="1:20">
+    <row r="19" spans="1:23">
       <c r="A19">
         <v>2487758</v>
       </c>
       <c r="B19" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C19" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D19" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E19" t="s">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="F19" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G19">
         <v>4</v>
@@ -3323,54 +3617,60 @@
         <v>1.46899559358928</v>
       </c>
       <c r="K19" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="L19">
         <v>4.53466666666667</v>
       </c>
       <c r="M19" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="N19" t="s">
-        <v>138</v>
+        <v>157</v>
       </c>
       <c r="O19" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="P19" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="Q19" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R19" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S19" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="T19" t="s">
-        <v>32</v>
+        <v>34</v>
+      </c>
+      <c r="V19">
+        <v>18</v>
+      </c>
+      <c r="W19" t="s">
+        <v>160</v>
       </c>
     </row>
-    <row r="20" spans="1:20">
+    <row r="20" spans="1:23">
       <c r="A20">
         <v>1113936</v>
       </c>
       <c r="B20" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="C20" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D20" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="E20" t="s">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="F20" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G20">
         <v>4</v>
@@ -3385,54 +3685,60 @@
         <v>1.58287650431256</v>
       </c>
       <c r="K20" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L20">
         <v>2.96397272727273</v>
       </c>
       <c r="M20" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="N20" t="s">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="O20" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="P20" t="s">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="Q20" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R20" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S20" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="T20" t="s">
-        <v>136</v>
+        <v>154</v>
+      </c>
+      <c r="V20">
+        <v>19</v>
+      </c>
+      <c r="W20" t="s">
+        <v>165</v>
       </c>
     </row>
-    <row r="21" spans="1:20">
+    <row r="21" spans="1:23">
       <c r="A21">
         <v>2333331</v>
       </c>
       <c r="B21" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="C21" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D21" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E21" t="s">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="F21" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G21">
         <v>9</v>
@@ -3447,54 +3753,60 @@
         <v>2.62924922385603</v>
       </c>
       <c r="K21" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="L21">
         <v>3.96298684210526</v>
       </c>
       <c r="M21" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="N21" t="s">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="O21" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="P21" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="Q21" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R21" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S21" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="T21" t="s">
-        <v>53</v>
+        <v>57</v>
+      </c>
+      <c r="V21">
+        <v>20</v>
+      </c>
+      <c r="W21" t="s">
+        <v>171</v>
       </c>
     </row>
-    <row r="22" spans="1:20">
+    <row r="22" spans="1:23">
       <c r="A22">
         <v>230996</v>
       </c>
       <c r="B22" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
       <c r="C22" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D22" t="s">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="E22" t="s">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="F22" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G22">
         <v>3</v>
@@ -3509,54 +3821,60 @@
         <v>0.856995717854035</v>
       </c>
       <c r="K22" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L22">
         <v>4.0315</v>
       </c>
       <c r="M22" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="N22" t="s">
-        <v>152</v>
+        <v>174</v>
       </c>
       <c r="O22" t="s">
-        <v>152</v>
+        <v>174</v>
       </c>
       <c r="P22" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="Q22" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R22" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S22" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="T22" t="s">
-        <v>32</v>
+        <v>34</v>
+      </c>
+      <c r="V22">
+        <v>21</v>
+      </c>
+      <c r="W22" t="s">
+        <v>176</v>
       </c>
     </row>
-    <row r="23" spans="1:20">
+    <row r="23" spans="1:23">
       <c r="A23">
         <v>2162294</v>
       </c>
       <c r="B23" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C23" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D23" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="E23" t="s">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="F23" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G23">
         <v>4</v>
@@ -3571,54 +3889,60 @@
         <v>0.818095992971064</v>
       </c>
       <c r="K23" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="L23">
         <v>3.11981904761905</v>
       </c>
       <c r="M23" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="N23" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="O23" t="s">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="P23" t="s">
-        <v>157</v>
+        <v>180</v>
       </c>
       <c r="Q23" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R23" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S23" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="T23" t="s">
-        <v>32</v>
+        <v>34</v>
+      </c>
+      <c r="V23">
+        <v>22</v>
+      </c>
+      <c r="W23" t="s">
+        <v>181</v>
       </c>
     </row>
-    <row r="24" spans="1:20">
+    <row r="24" spans="1:23">
       <c r="A24">
         <v>1206080</v>
       </c>
       <c r="B24" t="s">
-        <v>158</v>
+        <v>182</v>
       </c>
       <c r="C24" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D24" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="E24" t="s">
-        <v>159</v>
+        <v>183</v>
       </c>
       <c r="F24" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G24">
         <v>7</v>
@@ -3633,54 +3957,60 @@
         <v>2.34360693486494</v>
       </c>
       <c r="K24" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L24">
         <v>4.11657391304348</v>
       </c>
       <c r="M24" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="N24" t="s">
-        <v>160</v>
+        <v>184</v>
       </c>
       <c r="O24" t="s">
-        <v>161</v>
+        <v>185</v>
       </c>
       <c r="P24" t="s">
-        <v>162</v>
+        <v>186</v>
       </c>
       <c r="Q24" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R24" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S24" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="T24" t="s">
-        <v>32</v>
+        <v>34</v>
+      </c>
+      <c r="V24">
+        <v>23</v>
+      </c>
+      <c r="W24" t="s">
+        <v>187</v>
       </c>
     </row>
-    <row r="25" spans="1:20">
+    <row r="25" spans="1:23">
       <c r="A25">
         <v>672752</v>
       </c>
       <c r="B25" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C25" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D25" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E25" t="s">
-        <v>163</v>
+        <v>188</v>
       </c>
       <c r="F25" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G25">
         <v>4</v>
@@ -3695,54 +4025,60 @@
         <v>0.879506460812006</v>
       </c>
       <c r="K25" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="L25">
         <v>2.18741754385965</v>
       </c>
       <c r="M25" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="N25" t="s">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="O25" t="s">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="P25" t="s">
-        <v>166</v>
+        <v>191</v>
       </c>
       <c r="Q25" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R25" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S25" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="T25" t="s">
-        <v>42</v>
+        <v>45</v>
+      </c>
+      <c r="V25">
+        <v>24</v>
+      </c>
+      <c r="W25" t="s">
+        <v>192</v>
       </c>
     </row>
-    <row r="26" spans="1:20">
+    <row r="26" spans="1:23">
       <c r="A26">
         <v>1538388</v>
       </c>
       <c r="B26" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="C26" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D26" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="E26" t="s">
-        <v>167</v>
+        <v>193</v>
       </c>
       <c r="F26" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G26">
         <v>2</v>
@@ -3757,54 +4093,60 @@
         <v>0.276195427647939</v>
       </c>
       <c r="K26" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="L26">
         <v>3.85996666666667</v>
       </c>
       <c r="M26" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="N26" t="s">
-        <v>168</v>
+        <v>194</v>
       </c>
       <c r="O26" t="s">
-        <v>169</v>
+        <v>195</v>
       </c>
       <c r="P26" t="s">
-        <v>170</v>
+        <v>196</v>
       </c>
       <c r="Q26" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R26" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S26" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="T26" t="s">
-        <v>136</v>
+        <v>154</v>
+      </c>
+      <c r="V26">
+        <v>25</v>
+      </c>
+      <c r="W26" t="s">
+        <v>197</v>
       </c>
     </row>
-    <row r="27" spans="1:20">
+    <row r="27" spans="1:23">
       <c r="A27">
         <v>511037</v>
       </c>
       <c r="B27" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C27" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D27" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E27" t="s">
-        <v>171</v>
+        <v>198</v>
       </c>
       <c r="F27" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G27">
         <v>5</v>
@@ -3819,54 +4161,60 @@
         <v>1.41903527433887</v>
       </c>
       <c r="K27" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="L27">
         <v>2.72666</v>
       </c>
       <c r="M27" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="N27" t="s">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="O27" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="P27" t="s">
-        <v>174</v>
+        <v>201</v>
       </c>
       <c r="Q27" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R27" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S27" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="T27" t="s">
-        <v>32</v>
+        <v>34</v>
+      </c>
+      <c r="V27">
+        <v>26</v>
+      </c>
+      <c r="W27" t="s">
+        <v>202</v>
       </c>
     </row>
-    <row r="28" spans="1:20">
+    <row r="28" spans="1:23">
       <c r="A28">
         <v>971735</v>
       </c>
       <c r="B28" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
       <c r="C28" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D28" t="s">
-        <v>175</v>
+        <v>203</v>
       </c>
       <c r="E28" t="s">
-        <v>176</v>
+        <v>204</v>
       </c>
       <c r="F28" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G28">
         <v>6</v>
@@ -3881,54 +4229,60 @@
         <v>1.82404605002199</v>
       </c>
       <c r="K28" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="L28">
         <v>4.03586842105263</v>
       </c>
       <c r="M28" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="N28" t="s">
-        <v>177</v>
+        <v>205</v>
       </c>
       <c r="O28" t="s">
-        <v>178</v>
+        <v>206</v>
       </c>
       <c r="P28" t="s">
-        <v>179</v>
+        <v>207</v>
       </c>
       <c r="Q28" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R28" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S28" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="T28" t="s">
-        <v>32</v>
+        <v>34</v>
+      </c>
+      <c r="V28">
+        <v>27</v>
+      </c>
+      <c r="W28" t="s">
+        <v>208</v>
       </c>
     </row>
-    <row r="29" spans="1:20">
+    <row r="29" spans="1:23">
       <c r="A29">
         <v>3024418</v>
       </c>
       <c r="B29" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="C29" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D29" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="E29" t="s">
-        <v>180</v>
+        <v>209</v>
       </c>
       <c r="F29" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G29">
         <v>4</v>
@@ -3943,54 +4297,60 @@
         <v>0.847584679824574</v>
       </c>
       <c r="K29" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="L29">
         <v>3.86016666666666</v>
       </c>
       <c r="M29" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="N29" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="O29" t="s">
-        <v>182</v>
+        <v>211</v>
       </c>
       <c r="P29" t="s">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="Q29" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R29" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S29" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="T29" t="s">
-        <v>136</v>
+        <v>154</v>
+      </c>
+      <c r="V29">
+        <v>28</v>
+      </c>
+      <c r="W29" t="s">
+        <v>213</v>
       </c>
     </row>
-    <row r="30" spans="1:20">
+    <row r="30" spans="1:23">
       <c r="A30">
         <v>256924</v>
       </c>
       <c r="B30" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="C30" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D30" t="s">
-        <v>184</v>
+        <v>214</v>
       </c>
       <c r="E30" t="s">
-        <v>185</v>
+        <v>215</v>
       </c>
       <c r="F30" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G30">
         <v>9</v>
@@ -4005,54 +4365,60 @@
         <v>2.96558393572778</v>
       </c>
       <c r="K30" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="L30">
         <v>3.74200526315789</v>
       </c>
       <c r="M30" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N30" t="s">
-        <v>186</v>
+        <v>216</v>
       </c>
       <c r="O30" t="s">
-        <v>186</v>
+        <v>216</v>
       </c>
       <c r="P30" t="s">
-        <v>187</v>
+        <v>217</v>
       </c>
       <c r="Q30" t="s">
+        <v>31</v>
+      </c>
+      <c r="R30" t="s">
+        <v>32</v>
+      </c>
+      <c r="S30" t="s">
+        <v>33</v>
+      </c>
+      <c r="T30" t="s">
+        <v>34</v>
+      </c>
+      <c r="V30">
         <v>29</v>
       </c>
-      <c r="R30" t="s">
-        <v>30</v>
-      </c>
-      <c r="S30" t="s">
-        <v>31</v>
-      </c>
-      <c r="T30" t="s">
-        <v>32</v>
+      <c r="W30" t="s">
+        <v>218</v>
       </c>
     </row>
-    <row r="31" spans="1:20">
+    <row r="31" spans="1:23">
       <c r="A31">
         <v>2623413</v>
       </c>
       <c r="B31" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C31" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D31" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E31" t="s">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="F31" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G31">
         <v>8</v>
@@ -4067,54 +4433,60 @@
         <v>2.54232898941376</v>
       </c>
       <c r="K31" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="L31">
         <v>3.6144947368421</v>
       </c>
       <c r="M31" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="N31" t="s">
-        <v>189</v>
+        <v>220</v>
       </c>
       <c r="O31" t="s">
-        <v>190</v>
+        <v>221</v>
       </c>
       <c r="P31" t="s">
-        <v>191</v>
+        <v>222</v>
       </c>
       <c r="Q31" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R31" t="s">
+        <v>32</v>
+      </c>
+      <c r="S31" t="s">
+        <v>56</v>
+      </c>
+      <c r="T31" t="s">
+        <v>57</v>
+      </c>
+      <c r="V31">
         <v>30</v>
       </c>
-      <c r="S31" t="s">
-        <v>52</v>
-      </c>
-      <c r="T31" t="s">
-        <v>53</v>
+      <c r="W31" t="s">
+        <v>223</v>
       </c>
     </row>
-    <row r="32" spans="1:20">
+    <row r="32" spans="1:23">
       <c r="A32">
         <v>264145</v>
       </c>
       <c r="B32" t="s">
-        <v>192</v>
+        <v>224</v>
       </c>
       <c r="C32" t="s">
-        <v>193</v>
+        <v>225</v>
       </c>
       <c r="D32" t="s">
-        <v>194</v>
+        <v>226</v>
       </c>
       <c r="E32" t="s">
-        <v>194</v>
+        <v>226</v>
       </c>
       <c r="F32" t="s">
-        <v>193</v>
+        <v>225</v>
       </c>
       <c r="G32">
         <v>7</v>
@@ -4129,54 +4501,60 @@
         <v>2.28560053896231</v>
       </c>
       <c r="K32" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="L32">
         <v>3.08424736842105</v>
       </c>
       <c r="M32" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
       <c r="N32" t="s">
-        <v>196</v>
+        <v>228</v>
       </c>
       <c r="O32" t="s">
-        <v>196</v>
+        <v>228</v>
       </c>
       <c r="P32" t="s">
-        <v>197</v>
+        <v>229</v>
       </c>
       <c r="Q32" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R32" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
       <c r="S32" t="s">
-        <v>199</v>
+        <v>231</v>
       </c>
       <c r="T32" t="s">
-        <v>200</v>
+        <v>232</v>
+      </c>
+      <c r="V32">
+        <v>31</v>
+      </c>
+      <c r="W32" t="s">
+        <v>233</v>
       </c>
     </row>
-    <row r="33" spans="1:20">
+    <row r="33" spans="1:23">
       <c r="A33">
         <v>2416631</v>
       </c>
       <c r="B33" t="s">
-        <v>201</v>
+        <v>234</v>
       </c>
       <c r="C33" t="s">
-        <v>202</v>
+        <v>235</v>
       </c>
       <c r="D33" t="s">
-        <v>203</v>
+        <v>236</v>
       </c>
       <c r="E33" t="s">
-        <v>204</v>
+        <v>237</v>
       </c>
       <c r="F33" t="s">
-        <v>202</v>
+        <v>235</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -4191,54 +4569,60 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L33">
         <v>3.7007</v>
       </c>
       <c r="M33" t="s">
-        <v>205</v>
+        <v>238</v>
       </c>
       <c r="N33" t="s">
-        <v>206</v>
+        <v>239</v>
       </c>
       <c r="O33" t="s">
-        <v>206</v>
+        <v>239</v>
       </c>
       <c r="P33" t="s">
-        <v>207</v>
+        <v>240</v>
       </c>
       <c r="Q33" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R33" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
       <c r="S33" t="s">
-        <v>208</v>
+        <v>241</v>
       </c>
       <c r="T33" t="s">
-        <v>209</v>
+        <v>242</v>
+      </c>
+      <c r="V33">
+        <v>32</v>
+      </c>
+      <c r="W33" t="s">
+        <v>243</v>
       </c>
     </row>
-    <row r="34" spans="1:20">
+    <row r="34" spans="1:23">
       <c r="A34">
         <v>261223</v>
       </c>
       <c r="B34" t="s">
-        <v>210</v>
+        <v>244</v>
       </c>
       <c r="C34" t="s">
-        <v>202</v>
+        <v>235</v>
       </c>
       <c r="D34" t="s">
-        <v>203</v>
+        <v>236</v>
       </c>
       <c r="E34" t="s">
-        <v>211</v>
+        <v>245</v>
       </c>
       <c r="F34" t="s">
-        <v>202</v>
+        <v>235</v>
       </c>
       <c r="G34">
         <v>9</v>
@@ -4253,54 +4637,60 @@
         <v>2.97493750120193</v>
       </c>
       <c r="K34" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="L34">
         <v>2.53527888888889</v>
       </c>
       <c r="M34" t="s">
-        <v>212</v>
+        <v>246</v>
       </c>
       <c r="N34" t="s">
-        <v>213</v>
+        <v>247</v>
       </c>
       <c r="O34" t="s">
-        <v>213</v>
+        <v>247</v>
       </c>
       <c r="P34" t="s">
-        <v>214</v>
+        <v>248</v>
       </c>
       <c r="Q34" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R34" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
       <c r="S34" t="s">
-        <v>208</v>
+        <v>241</v>
       </c>
       <c r="T34" t="s">
-        <v>209</v>
+        <v>242</v>
+      </c>
+      <c r="V34">
+        <v>33</v>
+      </c>
+      <c r="W34" t="s">
+        <v>249</v>
       </c>
     </row>
-    <row r="35" spans="1:20">
+    <row r="35" spans="1:23">
       <c r="A35">
         <v>1113261</v>
       </c>
       <c r="B35" t="s">
-        <v>215</v>
+        <v>250</v>
       </c>
       <c r="C35" t="s">
-        <v>216</v>
+        <v>251</v>
       </c>
       <c r="D35" t="s">
-        <v>217</v>
+        <v>252</v>
       </c>
       <c r="E35" t="s">
-        <v>218</v>
+        <v>253</v>
       </c>
       <c r="F35" t="s">
-        <v>216</v>
+        <v>251</v>
       </c>
       <c r="G35">
         <v>4</v>
@@ -4315,54 +4705,60 @@
         <v>1.63373142064213</v>
       </c>
       <c r="K35" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="L35">
         <v>3.30649444444444</v>
       </c>
       <c r="M35" t="s">
-        <v>219</v>
+        <v>254</v>
       </c>
       <c r="N35" t="s">
-        <v>220</v>
+        <v>255</v>
       </c>
       <c r="O35" t="s">
-        <v>221</v>
+        <v>256</v>
       </c>
       <c r="P35" t="s">
-        <v>222</v>
+        <v>257</v>
       </c>
       <c r="Q35" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R35" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
       <c r="S35" t="s">
-        <v>223</v>
+        <v>258</v>
       </c>
       <c r="T35" t="s">
-        <v>224</v>
+        <v>259</v>
+      </c>
+      <c r="V35">
+        <v>34</v>
+      </c>
+      <c r="W35" t="s">
+        <v>260</v>
       </c>
     </row>
-    <row r="36" spans="1:20">
+    <row r="36" spans="1:23">
       <c r="A36">
         <v>2377552</v>
       </c>
       <c r="B36" t="s">
-        <v>225</v>
+        <v>261</v>
       </c>
       <c r="C36" t="s">
-        <v>226</v>
+        <v>262</v>
       </c>
       <c r="D36" t="s">
-        <v>227</v>
+        <v>263</v>
       </c>
       <c r="E36" t="s">
-        <v>228</v>
+        <v>264</v>
       </c>
       <c r="F36" t="s">
-        <v>226</v>
+        <v>262</v>
       </c>
       <c r="G36">
         <v>6</v>
@@ -4377,54 +4773,60 @@
         <v>1.68189906752261</v>
       </c>
       <c r="K36" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L36">
         <v>3.56068260869565</v>
       </c>
       <c r="M36" t="s">
-        <v>229</v>
+        <v>265</v>
       </c>
       <c r="N36" t="s">
+        <v>266</v>
+      </c>
+      <c r="O36" t="s">
+        <v>267</v>
+      </c>
+      <c r="P36" t="s">
+        <v>268</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>31</v>
+      </c>
+      <c r="R36" t="s">
         <v>230</v>
       </c>
-      <c r="O36" t="s">
-        <v>231</v>
-      </c>
-      <c r="P36" t="s">
-        <v>232</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>29</v>
-      </c>
-      <c r="R36" t="s">
-        <v>198</v>
-      </c>
       <c r="S36" t="s">
-        <v>233</v>
+        <v>269</v>
       </c>
       <c r="T36" t="s">
-        <v>234</v>
+        <v>270</v>
+      </c>
+      <c r="V36">
+        <v>35</v>
+      </c>
+      <c r="W36" t="s">
+        <v>271</v>
       </c>
     </row>
-    <row r="37" spans="1:20">
+    <row r="37" spans="1:23">
       <c r="A37">
         <v>2177658</v>
       </c>
       <c r="B37" t="s">
-        <v>235</v>
+        <v>272</v>
       </c>
       <c r="C37" t="s">
-        <v>226</v>
+        <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>236</v>
+        <v>273</v>
       </c>
       <c r="E37" t="s">
-        <v>237</v>
+        <v>274</v>
       </c>
       <c r="F37" t="s">
-        <v>226</v>
+        <v>262</v>
       </c>
       <c r="G37">
         <v>13</v>
@@ -4439,54 +4841,60 @@
         <v>3.5585186130489</v>
       </c>
       <c r="K37" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="L37">
         <v>2.71428285714286</v>
       </c>
       <c r="M37" t="s">
-        <v>238</v>
+        <v>275</v>
       </c>
       <c r="N37" t="s">
-        <v>239</v>
+        <v>276</v>
       </c>
       <c r="O37" t="s">
-        <v>240</v>
+        <v>277</v>
       </c>
       <c r="P37" t="s">
-        <v>241</v>
+        <v>278</v>
       </c>
       <c r="Q37" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R37" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
       <c r="S37" t="s">
-        <v>233</v>
+        <v>269</v>
       </c>
       <c r="T37" t="s">
-        <v>242</v>
+        <v>279</v>
+      </c>
+      <c r="V37">
+        <v>36</v>
+      </c>
+      <c r="W37" t="s">
+        <v>280</v>
       </c>
     </row>
-    <row r="38" spans="1:20">
+    <row r="38" spans="1:23">
       <c r="A38">
         <v>552679</v>
       </c>
       <c r="B38" t="s">
-        <v>243</v>
+        <v>281</v>
       </c>
       <c r="C38" t="s">
-        <v>244</v>
+        <v>282</v>
       </c>
       <c r="D38" t="s">
-        <v>245</v>
+        <v>283</v>
       </c>
       <c r="E38" t="s">
-        <v>246</v>
+        <v>284</v>
       </c>
       <c r="F38" t="s">
-        <v>244</v>
+        <v>282</v>
       </c>
       <c r="G38">
         <v>9</v>
@@ -4501,54 +4909,60 @@
         <v>2.25809602841205</v>
       </c>
       <c r="K38" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L38">
         <v>2.67418695652174</v>
       </c>
       <c r="M38" t="s">
-        <v>247</v>
+        <v>285</v>
       </c>
       <c r="N38" t="s">
-        <v>248</v>
+        <v>286</v>
       </c>
       <c r="O38" t="s">
-        <v>249</v>
+        <v>287</v>
       </c>
       <c r="P38" t="s">
-        <v>250</v>
+        <v>288</v>
       </c>
       <c r="Q38" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R38" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
       <c r="S38" t="s">
-        <v>199</v>
+        <v>231</v>
       </c>
       <c r="T38" t="s">
-        <v>200</v>
+        <v>232</v>
+      </c>
+      <c r="V38">
+        <v>37</v>
+      </c>
+      <c r="W38" t="s">
+        <v>289</v>
       </c>
     </row>
-    <row r="39" spans="1:20">
+    <row r="39" spans="1:23">
       <c r="A39">
         <v>2986259</v>
       </c>
       <c r="B39" t="s">
-        <v>251</v>
+        <v>290</v>
       </c>
       <c r="C39" t="s">
-        <v>202</v>
+        <v>235</v>
       </c>
       <c r="D39" t="s">
-        <v>203</v>
+        <v>236</v>
       </c>
       <c r="E39" t="s">
-        <v>252</v>
+        <v>291</v>
       </c>
       <c r="F39" t="s">
-        <v>202</v>
+        <v>235</v>
       </c>
       <c r="G39">
         <v>3</v>
@@ -4563,54 +4977,60 @@
         <v>0.856995717854035</v>
       </c>
       <c r="K39" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="L39">
         <v>3.38457142857143</v>
       </c>
       <c r="M39" t="s">
-        <v>205</v>
+        <v>238</v>
       </c>
       <c r="N39" t="s">
-        <v>253</v>
+        <v>292</v>
       </c>
       <c r="O39" t="s">
-        <v>254</v>
+        <v>293</v>
       </c>
       <c r="P39" t="s">
-        <v>255</v>
+        <v>294</v>
       </c>
       <c r="Q39" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R39" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
       <c r="S39" t="s">
-        <v>208</v>
+        <v>241</v>
       </c>
       <c r="T39" t="s">
-        <v>209</v>
+        <v>242</v>
+      </c>
+      <c r="V39">
+        <v>38</v>
+      </c>
+      <c r="W39" t="s">
+        <v>295</v>
       </c>
     </row>
-    <row r="40" spans="1:20">
+    <row r="40" spans="1:23">
       <c r="A40">
         <v>273218</v>
       </c>
       <c r="B40" t="s">
-        <v>256</v>
+        <v>296</v>
       </c>
       <c r="C40" t="s">
-        <v>193</v>
+        <v>225</v>
       </c>
       <c r="D40" t="s">
-        <v>257</v>
+        <v>297</v>
       </c>
       <c r="E40" t="s">
-        <v>257</v>
+        <v>297</v>
       </c>
       <c r="F40" t="s">
-        <v>193</v>
+        <v>225</v>
       </c>
       <c r="G40">
         <v>6</v>
@@ -4625,54 +5045,60 @@
         <v>1.53421902118034</v>
       </c>
       <c r="K40" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L40">
         <v>3.05323260869565</v>
       </c>
       <c r="M40" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
       <c r="N40" t="s">
-        <v>258</v>
+        <v>298</v>
       </c>
       <c r="O40" t="s">
-        <v>258</v>
+        <v>298</v>
       </c>
       <c r="P40" t="s">
-        <v>259</v>
+        <v>299</v>
       </c>
       <c r="Q40" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R40" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
       <c r="S40" t="s">
-        <v>260</v>
+        <v>300</v>
       </c>
       <c r="T40" t="s">
-        <v>261</v>
+        <v>301</v>
+      </c>
+      <c r="V40">
+        <v>39</v>
+      </c>
+      <c r="W40" t="s">
+        <v>302</v>
       </c>
     </row>
-    <row r="41" spans="1:20">
+    <row r="41" spans="1:23">
       <c r="A41">
         <v>3789120</v>
       </c>
       <c r="B41" t="s">
-        <v>192</v>
+        <v>224</v>
       </c>
       <c r="C41" t="s">
-        <v>244</v>
+        <v>282</v>
       </c>
       <c r="D41" t="s">
-        <v>262</v>
+        <v>303</v>
       </c>
       <c r="E41" t="s">
-        <v>263</v>
+        <v>304</v>
       </c>
       <c r="F41" t="s">
-        <v>244</v>
+        <v>282</v>
       </c>
       <c r="G41">
         <v>3</v>
@@ -4687,54 +5113,60 @@
         <v>0.90558726169826</v>
       </c>
       <c r="K41" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="L41">
         <v>2.97747333333333</v>
       </c>
       <c r="M41" t="s">
-        <v>212</v>
+        <v>246</v>
       </c>
       <c r="N41" t="s">
-        <v>264</v>
+        <v>305</v>
       </c>
       <c r="O41" t="s">
-        <v>265</v>
+        <v>306</v>
       </c>
       <c r="P41" t="s">
-        <v>266</v>
+        <v>307</v>
       </c>
       <c r="Q41" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R41" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
       <c r="S41" t="s">
-        <v>199</v>
+        <v>231</v>
       </c>
       <c r="T41" t="s">
-        <v>200</v>
+        <v>232</v>
+      </c>
+      <c r="V41">
+        <v>40</v>
+      </c>
+      <c r="W41" t="s">
+        <v>308</v>
       </c>
     </row>
-    <row r="42" spans="1:20">
+    <row r="42" spans="1:23">
       <c r="A42">
         <v>2403045</v>
       </c>
       <c r="B42" t="s">
-        <v>215</v>
+        <v>250</v>
       </c>
       <c r="C42" t="s">
-        <v>216</v>
+        <v>251</v>
       </c>
       <c r="D42" t="s">
-        <v>267</v>
+        <v>309</v>
       </c>
       <c r="E42" t="s">
-        <v>268</v>
+        <v>310</v>
       </c>
       <c r="F42" t="s">
-        <v>216</v>
+        <v>251</v>
       </c>
       <c r="G42">
         <v>7</v>
@@ -4749,54 +5181,60 @@
         <v>2.14051805627671</v>
       </c>
       <c r="K42" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="L42">
         <v>2.71334666666667</v>
       </c>
       <c r="M42" t="s">
-        <v>219</v>
+        <v>254</v>
       </c>
       <c r="N42" t="s">
-        <v>269</v>
+        <v>311</v>
       </c>
       <c r="O42" t="s">
-        <v>270</v>
+        <v>312</v>
       </c>
       <c r="P42" t="s">
-        <v>271</v>
+        <v>313</v>
       </c>
       <c r="Q42" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R42" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
       <c r="S42" t="s">
-        <v>223</v>
+        <v>258</v>
       </c>
       <c r="T42" t="s">
-        <v>224</v>
+        <v>259</v>
+      </c>
+      <c r="V42">
+        <v>41</v>
+      </c>
+      <c r="W42" t="s">
+        <v>314</v>
       </c>
     </row>
-    <row r="43" spans="1:20">
+    <row r="43" spans="1:23">
       <c r="A43">
         <v>2146369</v>
       </c>
       <c r="B43" t="s">
-        <v>158</v>
+        <v>182</v>
       </c>
       <c r="C43" t="s">
-        <v>216</v>
+        <v>251</v>
       </c>
       <c r="D43" t="s">
-        <v>272</v>
+        <v>315</v>
       </c>
       <c r="E43" t="s">
-        <v>273</v>
+        <v>316</v>
       </c>
       <c r="F43" t="s">
-        <v>216</v>
+        <v>251</v>
       </c>
       <c r="G43">
         <v>7</v>
@@ -4811,54 +5249,60 @@
         <v>2.35771746913015</v>
       </c>
       <c r="K43" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L43">
         <v>2.722385</v>
       </c>
       <c r="M43" t="s">
-        <v>274</v>
+        <v>317</v>
       </c>
       <c r="N43" t="s">
-        <v>275</v>
+        <v>318</v>
       </c>
       <c r="O43" t="s">
-        <v>276</v>
+        <v>319</v>
       </c>
       <c r="P43" t="s">
-        <v>277</v>
+        <v>320</v>
       </c>
       <c r="Q43" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R43" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
       <c r="S43" t="s">
-        <v>223</v>
+        <v>258</v>
       </c>
       <c r="T43" t="s">
-        <v>224</v>
+        <v>259</v>
+      </c>
+      <c r="V43">
+        <v>42</v>
+      </c>
+      <c r="W43" t="s">
+        <v>321</v>
       </c>
     </row>
-    <row r="44" spans="1:20">
+    <row r="44" spans="1:23">
       <c r="A44">
         <v>961547</v>
       </c>
       <c r="B44" t="s">
-        <v>278</v>
+        <v>322</v>
       </c>
       <c r="C44" t="s">
-        <v>202</v>
+        <v>235</v>
       </c>
       <c r="D44" t="s">
-        <v>279</v>
+        <v>323</v>
       </c>
       <c r="E44" t="s">
-        <v>279</v>
+        <v>323</v>
       </c>
       <c r="F44" t="s">
-        <v>202</v>
+        <v>235</v>
       </c>
       <c r="G44">
         <v>8</v>
@@ -4873,54 +5317,60 @@
         <v>2.5468465893424</v>
       </c>
       <c r="K44" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="L44">
         <v>3.39866984126984</v>
       </c>
       <c r="M44" t="s">
-        <v>280</v>
+        <v>324</v>
       </c>
       <c r="N44" t="s">
-        <v>281</v>
+        <v>325</v>
       </c>
       <c r="O44" t="s">
-        <v>282</v>
+        <v>326</v>
       </c>
       <c r="P44" t="s">
-        <v>283</v>
+        <v>327</v>
       </c>
       <c r="Q44" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R44" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
       <c r="S44" t="s">
-        <v>284</v>
+        <v>328</v>
       </c>
       <c r="T44" t="s">
-        <v>285</v>
+        <v>329</v>
+      </c>
+      <c r="V44">
+        <v>43</v>
+      </c>
+      <c r="W44" t="s">
+        <v>330</v>
       </c>
     </row>
-    <row r="45" spans="1:20">
+    <row r="45" spans="1:23">
       <c r="A45">
         <v>1845057</v>
       </c>
       <c r="B45" t="s">
-        <v>286</v>
+        <v>331</v>
       </c>
       <c r="C45" t="s">
-        <v>216</v>
+        <v>251</v>
       </c>
       <c r="D45" t="s">
-        <v>272</v>
+        <v>315</v>
       </c>
       <c r="E45" t="s">
-        <v>287</v>
+        <v>332</v>
       </c>
       <c r="F45" t="s">
-        <v>216</v>
+        <v>251</v>
       </c>
       <c r="G45">
         <v>9</v>
@@ -4935,54 +5385,60 @@
         <v>2.60138216209129</v>
       </c>
       <c r="K45" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="L45">
         <v>3.0165119047619</v>
       </c>
       <c r="M45" t="s">
-        <v>274</v>
+        <v>317</v>
       </c>
       <c r="N45" t="s">
-        <v>288</v>
+        <v>333</v>
       </c>
       <c r="O45" t="s">
-        <v>289</v>
+        <v>334</v>
       </c>
       <c r="P45" t="s">
-        <v>290</v>
+        <v>335</v>
       </c>
       <c r="Q45" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R45" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
       <c r="S45" t="s">
-        <v>223</v>
+        <v>258</v>
       </c>
       <c r="T45" t="s">
-        <v>224</v>
+        <v>259</v>
+      </c>
+      <c r="V45">
+        <v>44</v>
+      </c>
+      <c r="W45" t="s">
+        <v>336</v>
       </c>
     </row>
-    <row r="46" spans="1:20">
+    <row r="46" spans="1:23">
       <c r="A46">
         <v>556533</v>
       </c>
       <c r="B46" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
       <c r="C46" t="s">
-        <v>193</v>
+        <v>225</v>
       </c>
       <c r="D46" t="s">
-        <v>292</v>
+        <v>338</v>
       </c>
       <c r="E46" t="s">
-        <v>293</v>
+        <v>339</v>
       </c>
       <c r="F46" t="s">
-        <v>193</v>
+        <v>225</v>
       </c>
       <c r="G46">
         <v>5</v>
@@ -4997,54 +5453,60 @@
         <v>1.57889790298748</v>
       </c>
       <c r="K46" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="L46">
         <v>2.437585</v>
       </c>
       <c r="M46" t="s">
-        <v>294</v>
+        <v>340</v>
       </c>
       <c r="N46" t="s">
-        <v>295</v>
+        <v>341</v>
       </c>
       <c r="O46" t="s">
-        <v>296</v>
+        <v>342</v>
       </c>
       <c r="P46" t="s">
-        <v>297</v>
+        <v>343</v>
       </c>
       <c r="Q46" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R46" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
       <c r="S46" t="s">
-        <v>260</v>
+        <v>300</v>
       </c>
       <c r="T46" t="s">
-        <v>261</v>
+        <v>301</v>
+      </c>
+      <c r="V46">
+        <v>45</v>
+      </c>
+      <c r="W46" t="s">
+        <v>344</v>
       </c>
     </row>
-    <row r="47" spans="1:20">
+    <row r="47" spans="1:23">
       <c r="A47">
         <v>3338224</v>
       </c>
       <c r="B47" t="s">
-        <v>298</v>
+        <v>345</v>
       </c>
       <c r="C47" t="s">
-        <v>244</v>
+        <v>282</v>
       </c>
       <c r="D47" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="E47" t="s">
-        <v>300</v>
+        <v>347</v>
       </c>
       <c r="F47" t="s">
-        <v>244</v>
+        <v>282</v>
       </c>
       <c r="G47">
         <v>2</v>
@@ -5059,54 +5521,60 @@
         <v>0.266764987803026</v>
       </c>
       <c r="K47" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="L47">
         <v>3.39732727272727</v>
       </c>
       <c r="M47" t="s">
-        <v>301</v>
+        <v>348</v>
       </c>
       <c r="N47" t="s">
-        <v>302</v>
+        <v>349</v>
       </c>
       <c r="O47" t="s">
-        <v>303</v>
+        <v>350</v>
       </c>
       <c r="P47" t="s">
-        <v>304</v>
+        <v>351</v>
       </c>
       <c r="Q47" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R47" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
       <c r="S47" t="s">
-        <v>305</v>
+        <v>352</v>
       </c>
       <c r="T47" t="s">
-        <v>306</v>
+        <v>353</v>
+      </c>
+      <c r="V47">
+        <v>46</v>
+      </c>
+      <c r="W47" t="s">
+        <v>354</v>
       </c>
     </row>
-    <row r="48" spans="1:20">
+    <row r="48" spans="1:23">
       <c r="A48">
         <v>937444</v>
       </c>
       <c r="B48" t="s">
-        <v>307</v>
+        <v>355</v>
       </c>
       <c r="C48" t="s">
-        <v>193</v>
+        <v>225</v>
       </c>
       <c r="D48" t="s">
-        <v>308</v>
+        <v>356</v>
       </c>
       <c r="E48" t="s">
-        <v>309</v>
+        <v>357</v>
       </c>
       <c r="F48" t="s">
-        <v>193</v>
+        <v>225</v>
       </c>
       <c r="G48">
         <v>6</v>
@@ -5121,54 +5589,60 @@
         <v>1.53421902118034</v>
       </c>
       <c r="K48" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L48">
         <v>3.05323260869565</v>
       </c>
       <c r="M48" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
       <c r="N48" t="s">
-        <v>310</v>
+        <v>358</v>
       </c>
       <c r="O48" t="s">
-        <v>311</v>
+        <v>359</v>
       </c>
       <c r="P48" t="s">
-        <v>312</v>
+        <v>360</v>
       </c>
       <c r="Q48" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R48" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
       <c r="S48" t="s">
-        <v>313</v>
+        <v>361</v>
       </c>
       <c r="T48" t="s">
-        <v>314</v>
+        <v>362</v>
+      </c>
+      <c r="V48">
+        <v>47</v>
+      </c>
+      <c r="W48" t="s">
+        <v>363</v>
       </c>
     </row>
-    <row r="49" spans="1:20">
+    <row r="49" spans="1:23">
       <c r="A49">
         <v>914558</v>
       </c>
       <c r="B49" t="s">
-        <v>315</v>
+        <v>364</v>
       </c>
       <c r="C49" t="s">
-        <v>202</v>
+        <v>235</v>
       </c>
       <c r="D49" t="s">
-        <v>279</v>
+        <v>323</v>
       </c>
       <c r="E49" t="s">
-        <v>316</v>
+        <v>365</v>
       </c>
       <c r="F49" t="s">
-        <v>202</v>
+        <v>235</v>
       </c>
       <c r="G49">
         <v>9</v>
@@ -5183,54 +5657,60 @@
         <v>2.80459652970245</v>
       </c>
       <c r="K49" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L49">
         <v>3.25381136363636</v>
       </c>
       <c r="M49" t="s">
-        <v>280</v>
+        <v>324</v>
       </c>
       <c r="N49" t="s">
-        <v>317</v>
+        <v>366</v>
       </c>
       <c r="O49" t="s">
-        <v>318</v>
+        <v>367</v>
       </c>
       <c r="P49" t="s">
-        <v>319</v>
+        <v>368</v>
       </c>
       <c r="Q49" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R49" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
       <c r="S49" t="s">
-        <v>284</v>
+        <v>328</v>
       </c>
       <c r="T49" t="s">
-        <v>285</v>
+        <v>329</v>
+      </c>
+      <c r="V49">
+        <v>48</v>
+      </c>
+      <c r="W49" t="s">
+        <v>369</v>
       </c>
     </row>
-    <row r="50" spans="1:20">
+    <row r="50" spans="1:23">
       <c r="A50">
         <v>725035</v>
       </c>
       <c r="B50" t="s">
-        <v>320</v>
+        <v>370</v>
       </c>
       <c r="C50" t="s">
-        <v>244</v>
+        <v>282</v>
       </c>
       <c r="D50" t="s">
-        <v>262</v>
+        <v>303</v>
       </c>
       <c r="E50" t="s">
-        <v>321</v>
+        <v>371</v>
       </c>
       <c r="F50" t="s">
-        <v>244</v>
+        <v>282</v>
       </c>
       <c r="G50">
         <v>7</v>
@@ -5245,54 +5725,60 @@
         <v>1.96576780781922</v>
       </c>
       <c r="K50" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="L50">
         <v>2.64574090909091</v>
       </c>
       <c r="M50" t="s">
-        <v>212</v>
+        <v>246</v>
       </c>
       <c r="N50" t="s">
-        <v>322</v>
+        <v>372</v>
       </c>
       <c r="O50" t="s">
-        <v>323</v>
+        <v>373</v>
       </c>
       <c r="P50" t="s">
-        <v>324</v>
+        <v>374</v>
       </c>
       <c r="Q50" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R50" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
       <c r="S50" t="s">
-        <v>199</v>
+        <v>231</v>
       </c>
       <c r="T50" t="s">
-        <v>200</v>
+        <v>232</v>
+      </c>
+      <c r="V50">
+        <v>49</v>
+      </c>
+      <c r="W50" t="s">
+        <v>375</v>
       </c>
     </row>
-    <row r="51" spans="1:20">
+    <row r="51" spans="1:23">
       <c r="A51">
         <v>1351071</v>
       </c>
       <c r="B51" t="s">
-        <v>325</v>
+        <v>376</v>
       </c>
       <c r="C51" t="s">
-        <v>216</v>
+        <v>251</v>
       </c>
       <c r="D51" t="s">
-        <v>217</v>
+        <v>252</v>
       </c>
       <c r="E51" t="s">
-        <v>326</v>
+        <v>377</v>
       </c>
       <c r="F51" t="s">
-        <v>216</v>
+        <v>251</v>
       </c>
       <c r="G51">
         <v>7</v>
@@ -5307,54 +5793,60 @@
         <v>2.18375483192392</v>
       </c>
       <c r="K51" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="L51">
         <v>3.06282631578947</v>
       </c>
       <c r="M51" t="s">
-        <v>327</v>
+        <v>378</v>
       </c>
       <c r="N51" t="s">
-        <v>328</v>
+        <v>379</v>
       </c>
       <c r="O51" t="s">
-        <v>329</v>
+        <v>380</v>
       </c>
       <c r="P51" t="s">
-        <v>330</v>
+        <v>381</v>
       </c>
       <c r="Q51" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R51" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
       <c r="S51" t="s">
-        <v>223</v>
+        <v>258</v>
       </c>
       <c r="T51" t="s">
-        <v>224</v>
+        <v>259</v>
+      </c>
+      <c r="V51">
+        <v>50</v>
+      </c>
+      <c r="W51" t="s">
+        <v>382</v>
       </c>
     </row>
-    <row r="52" spans="1:20">
+    <row r="52" spans="1:23">
       <c r="A52">
         <v>2119153</v>
       </c>
       <c r="B52" t="s">
-        <v>331</v>
+        <v>383</v>
       </c>
       <c r="C52" t="s">
-        <v>226</v>
+        <v>262</v>
       </c>
       <c r="D52" t="s">
-        <v>332</v>
+        <v>384</v>
       </c>
       <c r="E52" t="s">
-        <v>333</v>
+        <v>385</v>
       </c>
       <c r="F52" t="s">
-        <v>226</v>
+        <v>262</v>
       </c>
       <c r="G52">
         <v>7</v>
@@ -5369,54 +5861,60 @@
         <v>2.44162987378722</v>
       </c>
       <c r="K52" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="L52">
         <v>3.00282307692308</v>
       </c>
       <c r="M52" t="s">
-        <v>334</v>
+        <v>386</v>
       </c>
       <c r="N52" t="s">
-        <v>335</v>
+        <v>387</v>
       </c>
       <c r="O52" t="s">
-        <v>336</v>
+        <v>388</v>
       </c>
       <c r="P52" t="s">
-        <v>337</v>
+        <v>389</v>
       </c>
       <c r="Q52" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R52" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
       <c r="S52" t="s">
-        <v>338</v>
+        <v>390</v>
       </c>
       <c r="T52" t="s">
-        <v>242</v>
+        <v>279</v>
+      </c>
+      <c r="V52">
+        <v>51</v>
+      </c>
+      <c r="W52" t="s">
+        <v>391</v>
       </c>
     </row>
-    <row r="53" spans="1:20">
+    <row r="53" spans="1:23">
       <c r="A53">
         <v>2075639</v>
       </c>
       <c r="B53" t="s">
-        <v>339</v>
+        <v>392</v>
       </c>
       <c r="C53" t="s">
-        <v>226</v>
+        <v>262</v>
       </c>
       <c r="D53" t="s">
-        <v>340</v>
+        <v>393</v>
       </c>
       <c r="E53" t="s">
-        <v>341</v>
+        <v>394</v>
       </c>
       <c r="F53" t="s">
-        <v>226</v>
+        <v>262</v>
       </c>
       <c r="G53">
         <v>8</v>
@@ -5431,54 +5929,60 @@
         <v>2.39086369685704</v>
       </c>
       <c r="K53" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="L53">
         <v>2.85833894736842</v>
       </c>
       <c r="M53" t="s">
-        <v>342</v>
+        <v>395</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>343</v>
+        <v>396</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>343</v>
+        <v>396</v>
       </c>
       <c r="P53" t="s">
-        <v>344</v>
+        <v>397</v>
       </c>
       <c r="Q53" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R53" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
       <c r="S53" t="s">
-        <v>345</v>
+        <v>398</v>
       </c>
       <c r="T53" t="s">
-        <v>346</v>
+        <v>399</v>
+      </c>
+      <c r="V53">
+        <v>52</v>
+      </c>
+      <c r="W53" t="s">
+        <v>400</v>
       </c>
     </row>
-    <row r="54" spans="1:20">
+    <row r="54" spans="1:23">
       <c r="A54">
         <v>3324843</v>
       </c>
       <c r="B54" t="s">
-        <v>215</v>
+        <v>250</v>
       </c>
       <c r="C54" t="s">
-        <v>216</v>
+        <v>251</v>
       </c>
       <c r="D54" t="s">
-        <v>347</v>
+        <v>401</v>
       </c>
       <c r="E54" t="s">
-        <v>348</v>
+        <v>402</v>
       </c>
       <c r="F54" t="s">
-        <v>216</v>
+        <v>251</v>
       </c>
       <c r="G54">
         <v>7</v>
@@ -5493,54 +5997,60 @@
         <v>1.65677964944704</v>
       </c>
       <c r="K54" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L54">
         <v>2.9016075</v>
       </c>
       <c r="M54" t="s">
-        <v>219</v>
+        <v>254</v>
       </c>
       <c r="N54" t="s">
-        <v>349</v>
+        <v>403</v>
       </c>
       <c r="O54" t="s">
-        <v>350</v>
+        <v>404</v>
       </c>
       <c r="P54" t="s">
-        <v>351</v>
+        <v>405</v>
       </c>
       <c r="Q54" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R54" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
       <c r="S54" t="s">
-        <v>223</v>
+        <v>258</v>
       </c>
       <c r="T54" t="s">
-        <v>224</v>
+        <v>259</v>
+      </c>
+      <c r="V54">
+        <v>53</v>
+      </c>
+      <c r="W54" t="s">
+        <v>406</v>
       </c>
     </row>
-    <row r="55" spans="1:20">
+    <row r="55" spans="1:23">
       <c r="A55">
         <v>3749927</v>
       </c>
       <c r="B55" t="s">
-        <v>298</v>
+        <v>345</v>
       </c>
       <c r="C55" t="s">
-        <v>244</v>
+        <v>282</v>
       </c>
       <c r="D55" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="E55" t="s">
-        <v>352</v>
+        <v>407</v>
       </c>
       <c r="F55" t="s">
-        <v>244</v>
+        <v>282</v>
       </c>
       <c r="G55">
         <v>3</v>
@@ -5555,54 +6065,60 @@
         <v>0.722857897732969</v>
       </c>
       <c r="K55" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="L55">
         <v>3.25007619047619</v>
       </c>
       <c r="M55" t="s">
-        <v>301</v>
+        <v>348</v>
       </c>
       <c r="N55" t="s">
+        <v>408</v>
+      </c>
+      <c r="O55" t="s">
+        <v>409</v>
+      </c>
+      <c r="P55" t="s">
+        <v>410</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>31</v>
+      </c>
+      <c r="R55" t="s">
+        <v>230</v>
+      </c>
+      <c r="S55" t="s">
+        <v>352</v>
+      </c>
+      <c r="T55" t="s">
         <v>353</v>
       </c>
-      <c r="O55" t="s">
-        <v>354</v>
-      </c>
-      <c r="P55" t="s">
-        <v>355</v>
-      </c>
-      <c r="Q55" t="s">
-        <v>29</v>
-      </c>
-      <c r="R55" t="s">
-        <v>198</v>
-      </c>
-      <c r="S55" t="s">
-        <v>305</v>
-      </c>
-      <c r="T55" t="s">
-        <v>306</v>
+      <c r="V55">
+        <v>54</v>
+      </c>
+      <c r="W55" t="s">
+        <v>411</v>
       </c>
     </row>
-    <row r="56" spans="1:20">
+    <row r="56" spans="1:23">
       <c r="A56">
         <v>2071296</v>
       </c>
       <c r="B56" t="s">
-        <v>356</v>
+        <v>412</v>
       </c>
       <c r="C56" t="s">
-        <v>244</v>
+        <v>282</v>
       </c>
       <c r="D56" t="s">
-        <v>262</v>
+        <v>303</v>
       </c>
       <c r="E56" t="s">
-        <v>357</v>
+        <v>413</v>
       </c>
       <c r="F56" t="s">
-        <v>244</v>
+        <v>282</v>
       </c>
       <c r="G56">
         <v>8</v>
@@ -5617,54 +6133,60 @@
         <v>1.98374067088286</v>
       </c>
       <c r="K56" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="L56">
         <v>2.86388596491228</v>
       </c>
       <c r="M56" t="s">
-        <v>212</v>
+        <v>246</v>
       </c>
       <c r="N56" t="s">
-        <v>358</v>
+        <v>414</v>
       </c>
       <c r="O56" t="s">
-        <v>359</v>
+        <v>415</v>
       </c>
       <c r="P56" t="s">
-        <v>360</v>
+        <v>416</v>
       </c>
       <c r="Q56" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R56" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
       <c r="S56" t="s">
-        <v>199</v>
+        <v>231</v>
       </c>
       <c r="T56" t="s">
-        <v>200</v>
+        <v>232</v>
+      </c>
+      <c r="V56">
+        <v>55</v>
+      </c>
+      <c r="W56" t="s">
+        <v>417</v>
       </c>
     </row>
-    <row r="57" spans="1:20">
+    <row r="57" spans="1:23">
       <c r="A57">
         <v>2492155</v>
       </c>
       <c r="B57" t="s">
-        <v>361</v>
+        <v>418</v>
       </c>
       <c r="C57" t="s">
-        <v>202</v>
+        <v>235</v>
       </c>
       <c r="D57" t="s">
-        <v>279</v>
+        <v>323</v>
       </c>
       <c r="E57" t="s">
-        <v>362</v>
+        <v>419</v>
       </c>
       <c r="F57" t="s">
-        <v>202</v>
+        <v>235</v>
       </c>
       <c r="G57">
         <v>12</v>
@@ -5679,54 +6201,60 @@
         <v>3.26804882875796</v>
       </c>
       <c r="K57" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="L57">
         <v>2.45418476190476</v>
       </c>
       <c r="M57" t="s">
-        <v>363</v>
+        <v>420</v>
       </c>
       <c r="N57" t="s">
-        <v>364</v>
+        <v>421</v>
       </c>
       <c r="O57" t="s">
-        <v>365</v>
+        <v>422</v>
       </c>
       <c r="P57" t="s">
-        <v>366</v>
+        <v>423</v>
       </c>
       <c r="Q57" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R57" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
       <c r="S57" t="s">
-        <v>284</v>
+        <v>328</v>
       </c>
       <c r="T57" t="s">
-        <v>285</v>
+        <v>329</v>
+      </c>
+      <c r="V57">
+        <v>56</v>
+      </c>
+      <c r="W57" t="s">
+        <v>424</v>
       </c>
     </row>
-    <row r="58" spans="1:20">
+    <row r="58" spans="1:23">
       <c r="A58">
         <v>1259265</v>
       </c>
       <c r="B58" t="s">
-        <v>367</v>
+        <v>425</v>
       </c>
       <c r="C58" t="s">
-        <v>226</v>
+        <v>262</v>
       </c>
       <c r="D58" t="s">
-        <v>368</v>
+        <v>426</v>
       </c>
       <c r="E58" t="s">
-        <v>369</v>
+        <v>427</v>
       </c>
       <c r="F58" t="s">
-        <v>226</v>
+        <v>262</v>
       </c>
       <c r="G58">
         <v>8</v>
@@ -5741,54 +6269,60 @@
         <v>1.91664227809565</v>
       </c>
       <c r="K58" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L58">
         <v>2.900805</v>
       </c>
       <c r="M58" t="s">
-        <v>247</v>
+        <v>285</v>
       </c>
       <c r="N58" t="s">
-        <v>370</v>
+        <v>428</v>
       </c>
       <c r="O58" t="s">
-        <v>371</v>
+        <v>429</v>
       </c>
       <c r="P58" t="s">
-        <v>372</v>
+        <v>430</v>
       </c>
       <c r="Q58" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R58" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
       <c r="S58" t="s">
-        <v>208</v>
+        <v>241</v>
       </c>
       <c r="T58" t="s">
-        <v>209</v>
+        <v>242</v>
+      </c>
+      <c r="V58">
+        <v>57</v>
+      </c>
+      <c r="W58" t="s">
+        <v>431</v>
       </c>
     </row>
-    <row r="59" spans="1:20">
+    <row r="59" spans="1:23">
       <c r="A59">
         <v>1168112</v>
       </c>
       <c r="B59" t="s">
-        <v>361</v>
+        <v>418</v>
       </c>
       <c r="C59" t="s">
-        <v>226</v>
+        <v>262</v>
       </c>
       <c r="D59" t="s">
-        <v>373</v>
+        <v>432</v>
       </c>
       <c r="E59" t="s">
-        <v>373</v>
+        <v>432</v>
       </c>
       <c r="F59" t="s">
-        <v>226</v>
+        <v>262</v>
       </c>
       <c r="G59">
         <v>8</v>
@@ -5803,54 +6337,60 @@
         <v>1.79564257617694</v>
       </c>
       <c r="K59" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="L59">
         <v>2.67532337662338</v>
       </c>
       <c r="M59" t="s">
-        <v>342</v>
+        <v>395</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>374</v>
+        <v>433</v>
       </c>
       <c r="O59" s="2" t="s">
-        <v>374</v>
+        <v>433</v>
       </c>
       <c r="P59" t="s">
-        <v>375</v>
+        <v>434</v>
       </c>
       <c r="Q59" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R59" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
       <c r="S59" t="s">
-        <v>284</v>
+        <v>328</v>
       </c>
       <c r="T59" t="s">
-        <v>285</v>
+        <v>329</v>
+      </c>
+      <c r="V59">
+        <v>58</v>
+      </c>
+      <c r="W59" t="s">
+        <v>435</v>
       </c>
     </row>
-    <row r="60" spans="1:20">
+    <row r="60" spans="1:23">
       <c r="A60">
         <v>767290</v>
       </c>
       <c r="B60" t="s">
-        <v>361</v>
+        <v>418</v>
       </c>
       <c r="C60" t="s">
-        <v>202</v>
+        <v>235</v>
       </c>
       <c r="D60" t="s">
-        <v>279</v>
+        <v>323</v>
       </c>
       <c r="E60" t="s">
-        <v>376</v>
+        <v>436</v>
       </c>
       <c r="F60" t="s">
-        <v>202</v>
+        <v>235</v>
       </c>
       <c r="G60">
         <v>4</v>
@@ -5865,54 +6405,60 @@
         <v>0.818095992971064</v>
       </c>
       <c r="K60" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="L60">
         <v>3.50727619047619</v>
       </c>
       <c r="M60" t="s">
-        <v>377</v>
+        <v>437</v>
       </c>
       <c r="N60" t="s">
-        <v>378</v>
+        <v>438</v>
       </c>
       <c r="O60" t="s">
-        <v>379</v>
+        <v>439</v>
       </c>
       <c r="P60" t="s">
-        <v>380</v>
+        <v>440</v>
       </c>
       <c r="Q60" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R60" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
       <c r="S60" t="s">
-        <v>284</v>
+        <v>328</v>
       </c>
       <c r="T60" t="s">
-        <v>285</v>
+        <v>329</v>
+      </c>
+      <c r="V60">
+        <v>59</v>
+      </c>
+      <c r="W60" t="s">
+        <v>441</v>
       </c>
     </row>
-    <row r="61" spans="1:20">
+    <row r="61" spans="1:23">
       <c r="A61">
         <v>877423</v>
       </c>
       <c r="B61" t="s">
-        <v>381</v>
+        <v>442</v>
       </c>
       <c r="C61" t="s">
-        <v>226</v>
+        <v>262</v>
       </c>
       <c r="D61" t="s">
-        <v>227</v>
+        <v>263</v>
       </c>
       <c r="E61" t="s">
-        <v>382</v>
+        <v>443</v>
       </c>
       <c r="F61" t="s">
-        <v>226</v>
+        <v>262</v>
       </c>
       <c r="G61">
         <v>11</v>
@@ -5927,42 +6473,48 @@
         <v>3.07610317099672</v>
       </c>
       <c r="K61" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="L61">
         <v>3.00784912280702</v>
       </c>
       <c r="M61" t="s">
-        <v>229</v>
+        <v>265</v>
       </c>
       <c r="N61" t="s">
-        <v>383</v>
+        <v>444</v>
       </c>
       <c r="O61" t="s">
-        <v>384</v>
+        <v>445</v>
       </c>
       <c r="P61" t="s">
-        <v>385</v>
+        <v>446</v>
       </c>
       <c r="Q61" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R61" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
       <c r="S61" t="s">
-        <v>233</v>
+        <v>269</v>
       </c>
       <c r="T61" t="s">
-        <v>242</v>
+        <v>279</v>
+      </c>
+      <c r="V61">
+        <v>60</v>
+      </c>
+      <c r="W61" t="s">
+        <v>447</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="N59" r:id="rId1" display="http://manynames.upf.edu/2399613_1168112_car.png"/>
-    <hyperlink ref="O59" r:id="rId1" display="http://manynames.upf.edu/2399613_1168112_car.png"/>
-    <hyperlink ref="N53" r:id="rId2" display="http://manynames.upf.edu/2341773_2075639_boat.png"/>
-    <hyperlink ref="O53" r:id="rId2" display="http://manynames.upf.edu/2341773_2075639_boat.png"/>
+    <hyperlink ref="N53" r:id="rId1" display="http://manynames.upf.edu/2341773_2075639_boat.png"/>
+    <hyperlink ref="O53" r:id="rId1" display="http://manynames.upf.edu/2341773_2075639_boat.png"/>
+    <hyperlink ref="N59" r:id="rId2" display="http://manynames.upf.edu/2399613_1168112_car.png"/>
+    <hyperlink ref="O59" r:id="rId2" display="http://manynames.upf.edu/2399613_1168112_car.png"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
